--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G2_task017.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G2_task017.xlsx
@@ -100,7 +100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
@@ -295,6 +295,50 @@
         <v>4.2594420068848402</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>40</v>
+      </c>
+      <c r="B5" s="0">
+        <v>68</v>
+      </c>
+      <c r="C5" s="0">
+        <v>40</v>
+      </c>
+      <c r="D5" s="0">
+        <v>93.245182912777111</v>
+      </c>
+      <c r="E5" s="0">
+        <v>487.32499999999999</v>
+      </c>
+      <c r="F5" s="0">
+        <v>151.13444246352407</v>
+      </c>
+      <c r="G5" s="0">
+        <v>7095.9563573272162</v>
+      </c>
+      <c r="H5" s="0">
+        <v>-1597.5608761259339</v>
+      </c>
+      <c r="I5" s="0">
+        <v>6.6299999999999999</v>
+      </c>
+      <c r="J5" s="0">
+        <v>19.335000000000001</v>
+      </c>
+      <c r="K5" s="0">
+        <v>3.0250000000000004</v>
+      </c>
+      <c r="L5" s="0">
+        <v>4.3550000000000004</v>
+      </c>
+      <c r="M5" s="0">
+        <v>279.74478077259778</v>
+      </c>
+      <c r="N5" s="0">
+        <v>4.2594420068848402</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>